--- a/Shallow_ML/Data.xlsx
+++ b/Shallow_ML/Data.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29010" windowHeight="12510"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="264">
   <si>
     <t>SMILES</t>
   </si>
@@ -330,6 +332,12 @@
     <t>[O-]C(=O)c1ccccc1SSc1ccccc1C([O-])=O</t>
   </si>
   <si>
+    <t>M(CTAB)</t>
+  </si>
+  <si>
+    <t>mM</t>
+  </si>
+  <si>
     <t>Propyl gallate</t>
   </si>
   <si>
@@ -339,6 +347,9 @@
     <t>Oc1cc(cc(O)c1O)C(=O)OCCC</t>
   </si>
   <si>
+    <t>propyl gallata</t>
+  </si>
+  <si>
     <t>Gallic acid</t>
   </si>
   <si>
@@ -558,9 +569,6 @@
     <t>C1=CC2=C3C(=C1)C=CC3=CC=C2</t>
   </si>
   <si>
-    <t>C1=CC2=C3C(=C1)C=CC3=CC=C3</t>
-  </si>
-  <si>
     <t>2-methyl naphtalene</t>
   </si>
   <si>
@@ -702,9 +710,6 @@
     <t>benzoate</t>
   </si>
   <si>
-    <t>c1cccc1C(=O)[O-]</t>
-  </si>
-  <si>
     <t>cinnamate</t>
   </si>
   <si>
@@ -729,9 +734,6 @@
     <t>Salicylate</t>
   </si>
   <si>
-    <t>c1ccc(O)c1C(=O)[O-]</t>
-  </si>
-  <si>
     <t>thymol</t>
   </si>
   <si>
@@ -805,6 +807,12 @@
   </si>
   <si>
     <t>CCCCCCCCCCCCCCCCCC(=O)[O-]</t>
+  </si>
+  <si>
+    <t>c1ccccc1C(=O)[O-]</t>
+  </si>
+  <si>
+    <t>c1cccc(O)c1C(=O)[O-]</t>
   </si>
 </sst>
 </file>
@@ -1156,19 +1164,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I606"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="48.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" customWidth="1"/>
-    <col min="8" max="9" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1">
+        <v>364.45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <f>1000*(1000*0.01)/B1</f>
+        <v>27.438606118809165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>0.1</v>
+      </c>
+      <c r="B6">
+        <f>1000*(1000*A6/100)/$C$5</f>
+        <v>4.4642857142857144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>0.2</v>
+      </c>
+      <c r="B7">
+        <f t="shared" ref="B7:B9" si="0">1000*(1000*A7/100)/$C$5</f>
+        <v>8.9285714285714288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>0.3</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>13.392857142857142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>0.35</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>15.625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <v>302.92090804548701</v>
+      </c>
+      <c r="B1">
+        <v>241.48788800838901</v>
+      </c>
+      <c r="C1">
+        <f>B1*1000</f>
+        <v>241487.88800838901</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>302.92729673324999</v>
+      </c>
+      <c r="B2">
+        <v>141.366699530613</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C7" si="0">B2*1000</f>
+        <v>141366.699530613</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>302.93837045870703</v>
+      </c>
+      <c r="B3">
+        <v>55.880915436266903</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>55880.915436266907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>303.05975552621402</v>
+      </c>
+      <c r="B4">
+        <v>21.322938524639198</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>21322.938524639198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>302.97244346011303</v>
+      </c>
+      <c r="B5">
+        <v>3.2137068680277601</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>3213.7068680277603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>303.73866007921902</v>
+      </c>
+      <c r="B6">
+        <v>4.1373410807913603E-2</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>41.373410807913601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>304.05085395459702</v>
+      </c>
+      <c r="B7">
+        <v>1.79004628936153E-3</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1.7900462893615299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I606"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34.1796875" customWidth="1"/>
+    <col min="2" max="2" width="48.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="23.1796875" customWidth="1"/>
+    <col min="6" max="6" width="28.81640625" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" customWidth="1"/>
+    <col min="8" max="9" width="28.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1197,7 +1376,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1224,7 +1403,7 @@
         <v>1.04477745095757</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1251,7 +1430,7 @@
         <v>1.94720301577807</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1278,7 +1457,7 @@
         <v>3.7072923637694997</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -1305,7 +1484,7 @@
         <v>68.649642579641593</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -1332,7 +1511,7 @@
         <v>7631.2102120417603</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1359,7 +1538,7 @@
         <v>40640</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1386,7 +1565,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -1413,7 +1592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -1440,7 +1619,7 @@
         <v>2.9816217976770303</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1467,7 +1646,7 @@
         <v>6.5143128711216898</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1494,7 +1673,7 @@
         <v>239.64150798318201</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -1521,7 +1700,7 @@
         <v>911.70432407783301</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -1548,7 +1727,7 @@
         <v>2907.3923918903997</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1575,7 +1754,7 @@
         <v>7205.5018426732695</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -1602,7 +1781,7 @@
         <v>2499.25298209318</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -1629,7 +1808,7 @@
         <v>803.72872297179401</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1835,7 @@
         <v>1.7794725491957899</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1683,7 +1862,7 @@
         <v>2.2585137927935999</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1710,7 +1889,7 @@
         <v>1.62930182406325</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1737,7 +1916,7 @@
         <v>2.6432069368316902</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1764,7 +1943,7 @@
         <v>3.5445682451253502</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1791,7 +1970,7 @@
         <v>4.2582442267948597</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1818,7 +1997,7 @@
         <v>3.7702174499056502</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1845,7 +2024,7 @@
         <v>3.3850750292029801</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1872,7 +2051,7 @@
         <v>2.29569143678677</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1899,7 +2078,7 @@
         <v>9.5073681372989505</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1926,7 +2105,7 @@
         <v>5.0378515589900204</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1953,7 +2132,7 @@
         <v>2.8682945457812901</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1980,7 +2159,7 @@
         <v>16.981647048252299</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -2007,7 +2186,7 @@
         <v>11.385344595201699</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -2034,7 +2213,7 @@
         <v>5.5073456734657196</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2061,7 +2240,7 @@
         <v>4.08931620091652</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -2088,7 +2267,7 @@
         <v>2.6246742744181799</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2115,7 +2294,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -2142,7 +2321,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2169,7 +2348,7 @@
         <v>10.86</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -2196,7 +2375,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -2223,7 +2402,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -2250,7 +2429,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -2277,7 +2456,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -2304,7 +2483,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -2331,7 +2510,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -2361,7 +2540,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -2391,7 +2570,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>34</v>
       </c>
@@ -2421,7 +2600,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -2451,7 +2630,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -2481,7 +2660,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -2511,7 +2690,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>34</v>
       </c>
@@ -2541,7 +2720,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -2571,7 +2750,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>36</v>
       </c>
@@ -2601,7 +2780,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>36</v>
       </c>
@@ -2631,7 +2810,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>36</v>
       </c>
@@ -2661,7 +2840,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -2691,7 +2870,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -2721,7 +2900,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>36</v>
       </c>
@@ -2751,7 +2930,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>36</v>
       </c>
@@ -2781,7 +2960,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>36</v>
       </c>
@@ -2811,7 +2990,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>36</v>
       </c>
@@ -2841,7 +3020,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>36</v>
       </c>
@@ -2871,7 +3050,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -2900,7 +3079,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -2929,7 +3108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -2958,7 +3137,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -2987,7 +3166,7 @@
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>55</v>
       </c>
@@ -3016,7 +3195,7 @@
         <v>12.34</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>41</v>
       </c>
@@ -3046,7 +3225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>41</v>
       </c>
@@ -3076,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>41</v>
       </c>
@@ -3106,7 +3285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>43</v>
       </c>
@@ -3136,7 +3315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>43</v>
       </c>
@@ -3166,7 +3345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>43</v>
       </c>
@@ -3196,7 +3375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>43</v>
       </c>
@@ -3226,7 +3405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>43</v>
       </c>
@@ -3256,7 +3435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -3286,7 +3465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -3316,7 +3495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>45</v>
       </c>
@@ -3346,7 +3525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>45</v>
       </c>
@@ -3376,7 +3555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>45</v>
       </c>
@@ -3406,7 +3585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>45</v>
       </c>
@@ -3436,7 +3615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>41</v>
       </c>
@@ -3466,7 +3645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>41</v>
       </c>
@@ -3496,7 +3675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>41</v>
       </c>
@@ -3526,7 +3705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>43</v>
       </c>
@@ -3556,7 +3735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>43</v>
       </c>
@@ -3586,7 +3765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>43</v>
       </c>
@@ -3616,7 +3795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>45</v>
       </c>
@@ -3646,7 +3825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>45</v>
       </c>
@@ -3676,7 +3855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>45</v>
       </c>
@@ -3706,7 +3885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>41</v>
       </c>
@@ -3736,7 +3915,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>43</v>
       </c>
@@ -3766,7 +3945,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3796,7 +3975,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>47</v>
       </c>
@@ -3826,7 +4005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>47</v>
       </c>
@@ -3856,7 +4035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -3886,7 +4065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>47</v>
       </c>
@@ -3916,7 +4095,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>47</v>
       </c>
@@ -3946,7 +4125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>47</v>
       </c>
@@ -3976,7 +4155,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>47</v>
       </c>
@@ -4006,7 +4185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>61</v>
       </c>
@@ -4037,7 +4216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>61</v>
       </c>
@@ -4067,7 +4246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -4097,7 +4276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>61</v>
       </c>
@@ -4127,7 +4306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>61</v>
       </c>
@@ -4157,7 +4336,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>61</v>
       </c>
@@ -4187,7 +4366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -4215,7 +4394,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>51</v>
       </c>
@@ -4243,7 +4422,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>51</v>
       </c>
@@ -4270,7 +4449,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>62</v>
       </c>
@@ -4298,7 +4477,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>62</v>
       </c>
@@ -4326,7 +4505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>62</v>
       </c>
@@ -4354,7 +4533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>62</v>
       </c>
@@ -4382,7 +4561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>64</v>
       </c>
@@ -4410,7 +4589,7 @@
         <v>83.87</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>64</v>
       </c>
@@ -4438,7 +4617,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>64</v>
       </c>
@@ -4466,7 +4645,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>64</v>
       </c>
@@ -4494,7 +4673,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>66</v>
       </c>
@@ -4522,7 +4701,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>66</v>
       </c>
@@ -4550,7 +4729,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>68</v>
       </c>
@@ -4577,7 +4756,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>69</v>
       </c>
@@ -4605,7 +4784,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>72</v>
       </c>
@@ -4632,7 +4811,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>74</v>
       </c>
@@ -4658,7 +4837,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>76</v>
       </c>
@@ -4684,7 +4863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>49</v>
       </c>
@@ -4712,7 +4891,7 @@
         <v>10.7006895569317</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>49</v>
       </c>
@@ -4740,7 +4919,7 @@
         <v>11.3539521295368</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>49</v>
       </c>
@@ -4768,7 +4947,7 @@
         <v>80.243851346073896</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>49</v>
       </c>
@@ -4796,7 +4975,7 @@
         <v>7249.2673666503497</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>49</v>
       </c>
@@ -4824,7 +5003,7 @@
         <v>195.182634871197</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>78</v>
       </c>
@@ -4852,7 +5031,7 @@
         <v>16.201634239927099</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>78</v>
       </c>
@@ -4880,7 +5059,7 @@
         <v>548239.83516736701</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>78</v>
       </c>
@@ -4908,7 +5087,7 @@
         <v>1690211.98337871</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>78</v>
       </c>
@@ -4936,7 +5115,7 @@
         <v>1052104.3676924801</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>80</v>
       </c>
@@ -4964,7 +5143,7 @@
         <v>601.74399458955395</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>80</v>
       </c>
@@ -4992,7 +5171,7 @@
         <v>934519.214560539</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>80</v>
       </c>
@@ -5020,7 +5199,7 @@
         <v>991570.34411669197</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>80</v>
       </c>
@@ -5048,7 +5227,7 @@
         <v>77572.159605721594</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>82</v>
       </c>
@@ -5076,7 +5255,7 @@
         <v>4.9528245211413395</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>82</v>
       </c>
@@ -5104,7 +5283,7 @@
         <v>617221.68590598903</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>82</v>
       </c>
@@ -5132,7 +5311,7 @@
         <v>9188.3026986310797</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>82</v>
       </c>
@@ -5160,7 +5339,7 @@
         <v>5719.4325303422102</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>83</v>
       </c>
@@ -5188,7 +5367,7 @@
         <v>35.003997734299794</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>83</v>
       </c>
@@ -5216,7 +5395,7 @@
         <v>2273095.3160389601</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>83</v>
       </c>
@@ -5244,7 +5423,7 @@
         <v>177827.94100389199</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>85</v>
       </c>
@@ -5272,7 +5451,7 @@
         <v>11.3539521295368</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>85</v>
       </c>
@@ -5300,7 +5479,7 @@
         <v>3056990.7009353801</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>85</v>
       </c>
@@ -5328,7 +5507,7 @@
         <v>3560.16878656058</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>85</v>
       </c>
@@ -5356,7 +5535,7 @@
         <v>20.535250264571502</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>87</v>
       </c>
@@ -5384,7 +5563,7 @@
         <v>173.368658316416</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>87</v>
       </c>
@@ -5412,7 +5591,7 @@
         <v>991570.34411669197</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>87</v>
       </c>
@@ -5440,7 +5619,7 @@
         <v>2351.3838413522003</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>87</v>
       </c>
@@ -5468,7 +5647,7 @@
         <v>11645.9915480647</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>89</v>
       </c>
@@ -5494,7 +5673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>91</v>
       </c>
@@ -5520,7 +5699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>94</v>
       </c>
@@ -5546,7 +5725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>95</v>
       </c>
@@ -5572,7 +5751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>97</v>
       </c>
@@ -5598,7 +5777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>99</v>
       </c>
@@ -5624,7 +5803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>101</v>
       </c>
@@ -5651,7 +5830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>101</v>
       </c>
@@ -5678,7 +5857,7 @@
         <v>3277.1682340647999</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>101</v>
       </c>
@@ -5705,7 +5884,7 @@
         <v>19008.620689655101</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>101</v>
       </c>
@@ -5732,7 +5911,7 @@
         <v>47887.931034482695</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>101</v>
       </c>
@@ -5759,7 +5938,7 @@
         <v>56854.754440961304</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>101</v>
       </c>
@@ -5786,7 +5965,7 @@
         <v>57843.521421107602</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>101</v>
       </c>
@@ -5813,7 +5992,7 @@
         <v>2931.9767567450499</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>101</v>
       </c>
@@ -5840,7 +6019,7 @@
         <v>19770.3756507463</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>101</v>
       </c>
@@ -5867,7 +6046,7 @@
         <v>42448.750351024901</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>101</v>
       </c>
@@ -5894,7 +6073,7 @@
         <v>55983.194003412995</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>101</v>
       </c>
@@ -5921,7 +6100,7 @@
         <v>64697.254444516402</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>101</v>
       </c>
@@ -5948,12 +6127,12 @@
         <v>29077.398310759701</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B170" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C170">
         <v>30</v>
@@ -5975,12 +6154,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B171" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C171">
         <v>30</v>
@@ -6002,12 +6181,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B172" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C172">
         <v>30</v>
@@ -6029,12 +6208,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B173" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C173">
         <v>30</v>
@@ -6056,12 +6235,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B174" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C174">
         <v>30</v>
@@ -6083,12 +6262,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B175" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C175">
         <v>30</v>
@@ -6110,12 +6289,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C176">
         <v>30</v>
@@ -6137,12 +6316,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B177" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C177">
         <v>30</v>
@@ -6164,12 +6343,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B178" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C178">
         <v>30</v>
@@ -6191,12 +6370,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B179" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C179">
         <v>30</v>
@@ -6218,12 +6397,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B180" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C180">
         <v>30</v>
@@ -6245,12 +6424,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B181" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C181">
         <v>30</v>
@@ -6272,12 +6451,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B182" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C182">
         <v>30</v>
@@ -6299,12 +6478,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B183" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C183">
         <v>15</v>
@@ -6326,12 +6505,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B184" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C184">
         <v>30</v>
@@ -6353,12 +6532,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B185" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C185">
         <v>40</v>
@@ -6380,12 +6559,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B186" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C186">
         <v>60</v>
@@ -6407,12 +6586,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B187" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C187">
         <v>15</v>
@@ -6434,12 +6613,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B188" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C188">
         <v>30</v>
@@ -6461,12 +6640,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B189" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C189">
         <v>40</v>
@@ -6488,12 +6667,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B190" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C190">
         <v>60</v>
@@ -6515,12 +6694,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B191" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C191">
         <v>15</v>
@@ -6542,12 +6721,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B192" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C192">
         <v>30</v>
@@ -6569,12 +6748,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B193" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C193">
         <v>40</v>
@@ -6596,12 +6775,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B194" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C194">
         <v>60</v>
@@ -6623,12 +6802,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B195" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C195">
         <v>15</v>
@@ -6650,12 +6829,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B196" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C196">
         <v>30</v>
@@ -6677,12 +6856,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B197" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C197">
         <v>40</v>
@@ -6704,12 +6883,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B198" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C198">
         <v>60</v>
@@ -6731,12 +6910,12 @@
         <v>181</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B199" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C199">
         <v>15</v>
@@ -6758,12 +6937,12 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B200" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C200">
         <v>30</v>
@@ -6785,12 +6964,12 @@
         <v>10.31</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B201" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C201">
         <v>40</v>
@@ -6812,12 +6991,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B202" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C202">
         <v>60</v>
@@ -6839,12 +7018,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B203" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C203">
         <v>15</v>
@@ -6866,12 +7045,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B204" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C204">
         <v>30</v>
@@ -6893,12 +7072,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B205" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C205">
         <v>40</v>
@@ -6920,12 +7099,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B206" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C206">
         <v>60</v>
@@ -6947,12 +7126,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B207" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C207">
         <v>15</v>
@@ -6974,12 +7153,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B208" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C208">
         <v>30</v>
@@ -7001,12 +7180,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B209" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C209">
         <v>40</v>
@@ -7028,12 +7207,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B210" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C210">
         <v>60</v>
@@ -7055,12 +7234,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B211" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C211">
         <v>15</v>
@@ -7082,12 +7261,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B212" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C212">
         <v>30</v>
@@ -7109,12 +7288,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B213" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C213">
         <v>40</v>
@@ -7136,12 +7315,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B214" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C214">
         <v>60</v>
@@ -7163,12 +7342,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B215" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C215">
         <v>15</v>
@@ -7190,12 +7369,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B216" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C216">
         <v>30</v>
@@ -7217,12 +7396,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B217" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C217">
         <v>40</v>
@@ -7244,12 +7423,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B218" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C218">
         <v>60</v>
@@ -7271,12 +7450,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B219" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -7298,12 +7477,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B220" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C220">
         <v>5</v>
@@ -7325,12 +7504,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B221" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C221">
         <v>25</v>
@@ -7352,12 +7531,12 @@
         <v>1.1838284581815901</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B222" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C222">
         <v>25</v>
@@ -7379,12 +7558,12 @@
         <v>1.23209162018893</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B223" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C223">
         <v>25</v>
@@ -7406,12 +7585,12 @@
         <v>1.29751506218585</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B224" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C224">
         <v>25</v>
@@ -7433,12 +7612,12 @@
         <v>1.3865479972319901</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B225" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C225">
         <v>25</v>
@@ -7460,12 +7639,12 @@
         <v>1.27411052892479</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B226" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C226">
         <v>25</v>
@@ -7487,12 +7666,12 @@
         <v>1.2596441504054099</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B227" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C227">
         <v>25</v>
@@ -7514,12 +7693,12 @@
         <v>1.48532087583343</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B228" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C228">
         <v>25</v>
@@ -7541,12 +7720,12 @@
         <v>1.59513257664355</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B229" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C229">
         <v>25</v>
@@ -7568,12 +7747,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B230" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C230">
         <v>25</v>
@@ -7595,12 +7774,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B231" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C231">
         <v>100</v>
@@ -7622,12 +7801,12 @@
         <v>116.06568382618499</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B232" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C232">
         <v>100</v>
@@ -7649,12 +7828,12 @@
         <v>3546.9760687242901</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B233" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C233">
         <v>100</v>
@@ -7676,12 +7855,12 @@
         <v>10223.477540370601</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B234" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C234">
         <v>100</v>
@@ -7703,12 +7882,12 @@
         <v>14667.6309475953</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B235" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C235">
         <v>100</v>
@@ -7730,12 +7909,12 @@
         <v>16.128329844736999</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B236" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C236">
         <v>100</v>
@@ -7757,12 +7936,12 @@
         <v>166.748512514807</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B237" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C237">
         <v>100</v>
@@ -7784,12 +7963,12 @@
         <v>1126.2214965519599</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B238" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C238">
         <v>100</v>
@@ -7811,12 +7990,12 @@
         <v>4089.1005635004999</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B239" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C239">
         <v>100</v>
@@ -7838,12 +8017,12 @@
         <v>4.9898045456805997</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B240" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C240">
         <v>100</v>
@@ -7865,12 +8044,12 @@
         <v>15.081066295319999</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B241" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C241">
         <v>100</v>
@@ -7892,12 +8071,12 @@
         <v>19.786890137762899</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B242" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C242">
         <v>100</v>
@@ -7919,12 +8098,12 @@
         <v>24.648629830407302</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B243" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C243">
         <v>100</v>
@@ -7946,12 +8125,12 @@
         <v>130.25776596716</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B244" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -7973,12 +8152,12 @@
         <v>2858.86306259094</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B245" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C245">
         <v>100</v>
@@ -8000,12 +8179,12 @@
         <v>8116.4395588012103</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B246" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C246">
         <v>100</v>
@@ -8027,12 +8206,12 @@
         <v>15826.896794927499</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B247" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C247">
         <v>100</v>
@@ -8054,12 +8233,12 @@
         <v>16.849464491854501</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B248" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C248">
         <v>100</v>
@@ -8081,12 +8260,12 @@
         <v>224.10583906743699</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B249" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C249">
         <v>100</v>
@@ -8108,12 +8287,12 @@
         <v>1189.9499659271701</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B250" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C250">
         <v>100</v>
@@ -8135,12 +8314,12 @@
         <v>6587.6591111673197</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B251" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C251">
         <v>100</v>
@@ -8162,12 +8341,12 @@
         <v>2.7998186967861498</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B252" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C252">
         <v>100</v>
@@ -8189,12 +8368,12 @@
         <v>26.667473556237699</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B253" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C253">
         <v>100</v>
@@ -8216,12 +8395,12 @@
         <v>135.80961360485401</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B254" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C254">
         <v>100</v>
@@ -8243,12 +8422,12 @@
         <v>817.30980106468496</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B255" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C255">
         <v>100</v>
@@ -8270,12 +8449,12 @@
         <v>166.31454521231399</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B256" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C256">
         <v>100</v>
@@ -8297,12 +8476,12 @@
         <v>1143.24559024269</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B257" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C257">
         <v>100</v>
@@ -8324,12 +8503,12 @@
         <v>14942.339672144</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B258" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C258">
         <v>100</v>
@@ -8351,12 +8530,12 @@
         <v>11742.685834509201</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B259" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C259">
         <v>100</v>
@@ -8378,12 +8557,12 @@
         <v>23.242298245944301</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B260" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C260">
         <v>100</v>
@@ -8405,12 +8584,12 @@
         <v>248.51284269805601</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B261" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C261">
         <v>100</v>
@@ -8432,12 +8611,12 @@
         <v>1851.15106175405</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B262" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C262">
         <v>100</v>
@@ -8459,12 +8638,12 @@
         <v>3814.1287482832099</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B263" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C263">
         <v>100</v>
@@ -8486,12 +8665,12 @@
         <v>5.4748483378970203</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B264" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C264">
         <v>100</v>
@@ -8513,12 +8692,12 @@
         <v>115.865326124376</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B265" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C265">
         <v>100</v>
@@ -8540,12 +8719,12 @@
         <v>269.29764661463599</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B266" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C266">
         <v>100</v>
@@ -8567,12 +8746,12 @@
         <v>1190.0943554067701</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B267" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C267">
         <v>100</v>
@@ -8594,12 +8773,12 @@
         <v>19.2962357090762</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B268" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C268">
         <v>100</v>
@@ -8621,12 +8800,12 @@
         <v>257.68141180412198</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B269" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C269">
         <v>100</v>
@@ -8648,12 +8827,12 @@
         <v>424.88943084066602</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B270" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C270">
         <v>100</v>
@@ -8675,12 +8854,12 @@
         <v>1805.8411353199201</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B271" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C271">
         <v>100</v>
@@ -8702,12 +8881,12 @@
         <v>3.9792579046113898</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B272" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C272">
         <v>100</v>
@@ -8729,12 +8908,12 @@
         <v>37.267327266961601</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B273" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C273">
         <v>100</v>
@@ -8756,12 +8935,12 @@
         <v>225.89777895757001</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B274" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -8783,12 +8962,12 @@
         <v>257.73823806889197</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B275" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -8810,12 +8989,12 @@
         <v>5.0425784541237197</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B276" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C276">
         <v>100</v>
@@ -8837,12 +9016,12 @@
         <v>23.1971999939684</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B277" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C277">
         <v>100</v>
@@ -8864,12 +9043,12 @@
         <v>80.933881052414193</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B278" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C278">
         <v>100</v>
@@ -8891,12 +9070,12 @@
         <v>97.317087306991198</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B279" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C279">
         <v>100</v>
@@ -8918,12 +9097,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B280" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C280">
         <v>100</v>
@@ -8945,12 +9124,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B281" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C281">
         <v>100</v>
@@ -8972,12 +9151,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B282" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C282">
         <v>100</v>
@@ -8999,12 +9178,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B283" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C283">
         <v>100</v>
@@ -9026,12 +9205,12 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B284" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C284">
         <v>100</v>
@@ -9053,12 +9232,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B285" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C285">
         <v>100</v>
@@ -9080,12 +9259,12 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B286" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C286">
         <v>100</v>
@@ -9107,12 +9286,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B287" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C287">
         <v>100</v>
@@ -9134,12 +9313,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B288" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C288">
         <v>100</v>
@@ -9161,12 +9340,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B289" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C289">
         <v>100</v>
@@ -9188,12 +9367,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B290" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C290">
         <v>101</v>
@@ -9215,12 +9394,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B291" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C291">
         <v>102</v>
@@ -9242,12 +9421,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B292" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C292">
         <v>103</v>
@@ -9269,12 +9448,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B293" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C293">
         <v>104</v>
@@ -9296,12 +9475,12 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B294" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C294">
         <v>105</v>
@@ -9323,12 +9502,12 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B295" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C295">
         <v>106</v>
@@ -9350,12 +9529,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B296" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C296">
         <v>107</v>
@@ -9377,12 +9556,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B297" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C297">
         <v>60</v>
@@ -9404,12 +9583,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B298" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C298">
         <v>60</v>
@@ -9432,12 +9611,12 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B299" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C299">
         <v>60</v>
@@ -9460,12 +9639,12 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B300" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C300">
         <v>80</v>
@@ -9487,12 +9666,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B301" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C301">
         <v>80</v>
@@ -9515,12 +9694,12 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B302" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C302">
         <v>80</v>
@@ -9543,12 +9722,12 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B303" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C303">
         <v>12.5</v>
@@ -9570,12 +9749,12 @@
         <v>0.769657270213014</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B304" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C304">
         <v>12.5</v>
@@ -9597,12 +9776,12 @@
         <v>2.3618053543316702</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B305" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C305">
         <v>12.5</v>
@@ -9624,12 +9803,12 @@
         <v>22314.9173309529</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B306" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C306">
         <v>12.5</v>
@@ -9651,12 +9830,12 @@
         <v>52961.431326218197</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B307" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C307">
         <v>12.5</v>
@@ -9678,12 +9857,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B308" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C308">
         <v>12.5</v>
@@ -9705,12 +9884,12 @@
         <v>1.3433081483906499</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B309" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C309">
         <v>12.5</v>
@@ -9732,12 +9911,12 @@
         <v>41.901632747734297</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B310" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C310">
         <v>12.5</v>
@@ -9759,12 +9938,12 @@
         <v>551.32212006895395</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B311" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C311">
         <v>12.5</v>
@@ -9786,12 +9965,12 @@
         <v>1.4167116853680999</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B312" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C312">
         <v>12.5</v>
@@ -9813,12 +9992,12 @@
         <v>1.3433081483906499</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B313" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C313">
         <v>12.5</v>
@@ -9840,12 +10019,12 @@
         <v>41.901632747734297</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B314" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C314">
         <v>12.5</v>
@@ -9867,12 +10046,12 @@
         <v>551.32212006895395</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B315" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C315">
         <v>12.5</v>
@@ -9894,12 +10073,12 @@
         <v>1.2605550464622299</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B316" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C316">
         <v>12.5</v>
@@ -9921,12 +10100,12 @@
         <v>1.1244496684140899</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B317" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C317">
         <v>12.5</v>
@@ -9948,12 +10127,12 @@
         <v>1.0474903402498099</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B318" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C318">
         <v>12.5</v>
@@ -9975,12 +10154,12 @@
         <v>0.95486974360386601</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B319" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C319">
         <v>250</v>
@@ -10002,12 +10181,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B320" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C320">
         <v>250</v>
@@ -10029,12 +10208,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B321" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C321">
         <v>250</v>
@@ -10056,12 +10235,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B322" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C322">
         <v>250</v>
@@ -10083,12 +10262,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B323" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C323">
         <v>250</v>
@@ -10110,12 +10289,12 @@
         <v>3.5480937979510601</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B324" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C324">
         <v>250</v>
@@ -10137,12 +10316,12 @@
         <v>3.78971541987287</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B325" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C325">
         <v>250</v>
@@ -10164,12 +10343,12 @@
         <v>4.4497016139996797</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B326" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C326">
         <v>250</v>
@@ -10191,12 +10370,12 @@
         <v>6.4779987633229101</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C327">
         <v>250</v>
@@ -10218,12 +10397,12 @@
         <v>3.6937095494018402</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C328">
         <v>250</v>
@@ -10245,12 +10424,12 @@
         <v>4.5629651764153696</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C329">
         <v>250</v>
@@ -10272,12 +10451,12 @@
         <v>8.2728080965435904</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B330" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C330">
         <v>250</v>
@@ -10299,12 +10478,12 @@
         <v>3.6137047586639901</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B331" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C331">
         <v>250</v>
@@ -10326,12 +10505,12 @@
         <v>4.1815462850892899</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B332" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C332">
         <v>250</v>
@@ -10353,12 +10532,12 @@
         <v>6.3383987284507999</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B333" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C333">
         <v>250</v>
@@ -10380,12 +10559,12 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B334" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C334">
         <v>250</v>
@@ -10407,12 +10586,12 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B335" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C335">
         <v>250</v>
@@ -10434,12 +10613,12 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B336" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C336">
         <v>250</v>
@@ -10461,12 +10640,12 @@
         <v>13.07</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B337" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C337">
         <v>250</v>
@@ -10488,12 +10667,12 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B338" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C338">
         <v>250</v>
@@ -10515,12 +10694,12 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B339" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C339">
         <v>250</v>
@@ -10542,12 +10721,12 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B340" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C340">
         <v>250</v>
@@ -10569,12 +10748,12 @@
         <v>19.190000000000001</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B341" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C341">
         <v>250</v>
@@ -10596,12 +10775,12 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B342" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C342">
         <v>250</v>
@@ -10623,12 +10802,12 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B343" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C343">
         <v>250</v>
@@ -10650,12 +10829,12 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B344" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C344">
         <v>250</v>
@@ -10677,12 +10856,12 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B345" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C345">
         <v>250</v>
@@ -10704,12 +10883,12 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B346" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C346">
         <v>250</v>
@@ -10731,12 +10910,12 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B347" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C347">
         <v>250</v>
@@ -10758,12 +10937,12 @@
         <v>10.45</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B348" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C348">
         <v>250</v>
@@ -10785,12 +10964,12 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B349" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C349">
         <v>250</v>
@@ -10812,12 +10991,12 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B350" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C350">
         <v>250</v>
@@ -10839,12 +11018,12 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B351" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C351">
         <v>250</v>
@@ -10866,12 +11045,12 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B352" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C352">
         <v>250</v>
@@ -10893,12 +11072,12 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B353" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C353">
         <v>250</v>
@@ -10920,12 +11099,12 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B354" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C354">
         <v>250</v>
@@ -10947,12 +11126,12 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B355" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C355">
         <v>250</v>
@@ -10974,12 +11153,12 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B356" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C356">
         <v>250</v>
@@ -11001,12 +11180,12 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B357" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C357">
         <v>250</v>
@@ -11028,12 +11207,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B358" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C358">
         <v>250</v>
@@ -11055,12 +11234,12 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B359" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C359">
         <v>250</v>
@@ -11082,12 +11261,12 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B360" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C360">
         <v>250</v>
@@ -11109,12 +11288,12 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B361" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C361">
         <v>250</v>
@@ -11136,12 +11315,12 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B362" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C362">
         <v>250</v>
@@ -11163,12 +11342,12 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B363" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C363">
         <v>250</v>
@@ -11190,12 +11369,12 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B364" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C364">
         <v>251</v>
@@ -11217,12 +11396,12 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B365" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C365">
         <v>250</v>
@@ -11244,12 +11423,12 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B366" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C366">
         <v>250</v>
@@ -11271,12 +11450,12 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B367" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C367">
         <v>250</v>
@@ -11298,12 +11477,12 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B368" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C368">
         <v>100</v>
@@ -11325,12 +11504,12 @@
         <v>1.5216214557316701</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B369" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C369">
         <v>100</v>
@@ -11352,12 +11531,12 @@
         <v>42.768647950025802</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B370" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C370">
         <v>100</v>
@@ -11379,12 +11558,12 @@
         <v>1245.96883400351</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B371" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C371">
         <v>100</v>
@@ -11406,12 +11585,12 @@
         <v>14410.683376041901</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B372" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C372">
         <v>100</v>
@@ -11433,12 +11612,12 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B373" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C373">
         <v>100</v>
@@ -11460,12 +11639,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B374" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C374">
         <v>50</v>
@@ -11487,12 +11666,12 @@
         <v>1.1898395721925099</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B375" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C375">
         <v>50</v>
@@ -11514,12 +11693,12 @@
         <v>1.5534759358288699</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B376" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C376">
         <v>50</v>
@@ -11541,12 +11720,12 @@
         <v>1.9812834224598901</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B377" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C377">
         <v>50</v>
@@ -11568,12 +11747,12 @@
         <v>2.22727272727272</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B378" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C378">
         <v>25</v>
@@ -11595,12 +11774,12 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B379" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C379">
         <v>50</v>
@@ -11622,12 +11801,12 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B380" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C380">
         <v>75</v>
@@ -11649,12 +11828,12 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B381" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C381">
         <v>100</v>
@@ -11676,12 +11855,12 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B382" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C382">
         <v>25</v>
@@ -11703,12 +11882,12 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B383" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C383">
         <v>50</v>
@@ -11730,12 +11909,12 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B384" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C384">
         <v>75</v>
@@ -11757,12 +11936,12 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B385" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C385">
         <v>100</v>
@@ -11784,12 +11963,12 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B386" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C386">
         <v>25</v>
@@ -11811,12 +11990,12 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B387" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C387">
         <v>50</v>
@@ -11838,12 +12017,12 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B388" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C388">
         <v>75</v>
@@ -11865,12 +12044,12 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B389" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C389">
         <v>10</v>
@@ -11892,7 +12071,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="390" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>97</v>
       </c>
@@ -11919,7 +12098,7 @@
         <v>1.4307229891937501</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>97</v>
       </c>
@@ -11946,7 +12125,7 @@
         <v>8.5769589859089397</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>97</v>
       </c>
@@ -11973,7 +12152,7 @@
         <v>4410.0594541767405</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>97</v>
       </c>
@@ -12000,12 +12179,12 @@
         <v>378248.99063893902</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B394" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C394">
         <v>100</v>
@@ -12027,12 +12206,12 @@
         <v>1.5058363542798401</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B395" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C395">
         <v>100</v>
@@ -12054,12 +12233,12 @@
         <v>3.0823992397451501</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B396" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C396">
         <v>100</v>
@@ -12081,12 +12260,12 @@
         <v>238.65897868585802</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B397" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C397">
         <v>100</v>
@@ -12108,7 +12287,7 @@
         <v>39810.717055349698</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>89</v>
       </c>
@@ -12135,7 +12314,7 @@
         <v>1.58489319246111</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>89</v>
       </c>
@@ -12162,7 +12341,7 @@
         <v>21.5443469003188</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>89</v>
       </c>
@@ -12189,7 +12368,7 @@
         <v>2154.4346900318797</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>89</v>
       </c>
@@ -12216,7 +12395,7 @@
         <v>175567.6291275</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>91</v>
       </c>
@@ -12243,7 +12422,7 @@
         <v>1.35935639087852</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>91</v>
       </c>
@@ -12270,7 +12449,7 @@
         <v>11.659144011798301</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>91</v>
       </c>
@@ -12297,7 +12476,7 @@
         <v>488.52735715193802</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>91</v>
       </c>
@@ -12324,12 +12503,12 @@
         <v>135935.639087852</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B406" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C406">
         <v>100</v>
@@ -12351,12 +12530,12 @@
         <v>1.7556762912750001</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B407" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C407">
         <v>100</v>
@@ -12378,12 +12557,12 @@
         <v>9.5011850731814302</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B408" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C408">
         <v>100</v>
@@ -12405,12 +12584,12 @@
         <v>90.272517794845697</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B409" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C409">
         <v>100</v>
@@ -12432,12 +12611,12 @@
         <v>194486.24389373601</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B410" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C410">
         <v>100</v>
@@ -12459,12 +12638,12 @@
         <v>1.2031003019517901</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B411" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C411">
         <v>100</v>
@@ -12486,12 +12665,12 @@
         <v>1.7756297160536001</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B412" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C412">
         <v>100</v>
@@ -12513,12 +12692,12 @@
         <v>25.601575761673399</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B413" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C413">
         <v>100</v>
@@ -12540,12 +12719,12 @@
         <v>4023.2089338893202</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B414" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C414">
         <v>100</v>
@@ -12567,12 +12746,12 @@
         <v>1.1811510484746299</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B415" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C415">
         <v>100</v>
@@ -12594,12 +12773,12 @@
         <v>2.45801497990908</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B416" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C416">
         <v>100</v>
@@ -12621,12 +12800,12 @@
         <v>578.27627603924202</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B417" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C417">
         <v>100</v>
@@ -12648,12 +12827,12 @@
         <v>75513.883368275405</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C418">
         <v>100</v>
@@ -12675,12 +12854,12 @@
         <v>1.2987522053070799</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C419">
         <v>100</v>
@@ -12702,12 +12881,12 @@
         <v>14.210431830705099</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C420">
         <v>100</v>
@@ -12729,12 +12908,12 @@
         <v>3163.5080064568401</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C421">
         <v>100</v>
@@ -12756,12 +12935,12 @@
         <v>36913.139916211898</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B422" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C422">
         <v>100</v>
@@ -12783,12 +12962,12 @@
         <v>1.4347439811676101</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B423" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C423">
         <v>100</v>
@@ -12810,12 +12989,12 @@
         <v>11.133375896041201</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B424" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C424">
         <v>100</v>
@@ -12837,12 +13016,12 @@
         <v>143.51161006070799</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B425" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C425">
         <v>100</v>
@@ -12864,12 +13043,12 @@
         <v>5177.9398327663394</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B426" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C426">
         <v>100</v>
@@ -12891,12 +13070,12 @@
         <v>1.69289237996942</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B427" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C427">
         <v>100</v>
@@ -12918,12 +13097,12 @@
         <v>5.9439295993342798</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B428" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C428">
         <v>100</v>
@@ -12945,12 +13124,12 @@
         <v>1781.1639971033399</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B429" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C429">
         <v>100</v>
@@ -12972,12 +13151,12 @@
         <v>105460.101651629</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B430" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C430">
         <v>75</v>
@@ -12999,12 +13178,12 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B431" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C431">
         <v>60</v>
@@ -13026,12 +13205,12 @@
         <v>77781</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B432" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C432">
         <v>60</v>
@@ -13053,12 +13232,12 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B433" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C433">
         <v>60</v>
@@ -13080,12 +13259,12 @@
         <v>317</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B434" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C434">
         <v>60</v>
@@ -13107,12 +13286,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B435" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C435">
         <v>60</v>
@@ -13134,12 +13313,12 @@
         <v>14008</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B436" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C436">
         <v>60</v>
@@ -13161,12 +13340,12 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B437" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -13188,12 +13367,12 @@
         <v>1.0178699841461201</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B438" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C438">
         <v>20</v>
@@ -13215,12 +13394,12 @@
         <v>70.170382867038199</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B439" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C439">
         <v>20</v>
@@ -13242,12 +13421,12 @@
         <v>1.0360593046256299</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B440" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C440">
         <v>20</v>
@@ -13269,12 +13448,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B441" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C441">
         <v>20</v>
@@ -13296,12 +13475,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B442" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C442">
         <v>20</v>
@@ -13323,12 +13502,12 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B443" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C443">
         <v>300</v>
@@ -13350,12 +13529,12 @@
         <v>900</v>
       </c>
     </row>
-    <row r="444" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B444" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C444">
         <v>150</v>
@@ -13377,12 +13556,12 @@
         <v>1.99335963763758</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B445" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C445">
         <v>150</v>
@@ -13404,12 +13583,12 @@
         <v>78.323663383600092</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B446" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C446">
         <v>150</v>
@@ -13431,12 +13610,12 @@
         <v>2891.8660056705598</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B447" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C447">
         <v>150</v>
@@ -13458,12 +13637,12 @@
         <v>538.09543123252899</v>
       </c>
     </row>
-    <row r="448" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B448" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C448">
         <v>50</v>
@@ -13485,12 +13664,12 @@
         <v>1.1849379419472801</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B449" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C449">
         <v>50</v>
@@ -13512,12 +13691,12 @@
         <v>1.2764179399693401</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B450" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C450">
         <v>50</v>
@@ -13539,12 +13718,12 @@
         <v>1.7026652821045301</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B451" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C451">
         <v>50</v>
@@ -13566,12 +13745,12 @@
         <v>1.98125896256737</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B452" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C452">
         <v>50</v>
@@ -13593,12 +13772,12 @@
         <v>1.23992647058823</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B453" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C453">
         <v>50</v>
@@ -13620,12 +13799,12 @@
         <v>1.28426470588235</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B454" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C454">
         <v>50</v>
@@ -13647,12 +13826,12 @@
         <v>1.3806617647058801</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B455" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C455">
         <v>50</v>
@@ -13674,12 +13853,12 @@
         <v>2.07794117647058</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B456" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C456">
         <v>50</v>
@@ -13701,12 +13880,12 @@
         <v>1.5194805194805301</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B457" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C457">
         <v>50</v>
@@ -13728,12 +13907,12 @@
         <v>1.9285714285714399</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B458" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C458">
         <v>50</v>
@@ -13755,12 +13934,12 @@
         <v>7.0324675324675603</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B459" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C459">
         <v>50</v>
@@ -13782,12 +13961,12 @@
         <v>21.837662337662302</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B460" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C460">
         <v>83.015873015872998</v>
@@ -13809,12 +13988,12 @@
         <v>0.74584182366527296</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B461" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C461">
         <v>111.98412698412599</v>
@@ -13836,12 +14015,12 @@
         <v>3.5793333012226598</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B462" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C462">
         <v>134.60317460317401</v>
@@ -13863,12 +14042,12 @@
         <v>9.4987626481452594</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B463" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C463">
         <v>153.65079365079299</v>
@@ -13890,12 +14069,12 @@
         <v>13.960064096812699</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B464" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C464">
         <v>169.12698412698401</v>
@@ -13917,12 +14096,12 @@
         <v>19.409815629279201</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B465" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C465">
         <v>82.2222222222222</v>
@@ -13944,12 +14123,12 @@
         <v>166.45596868565499</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B466" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C466">
         <v>112.380952380952</v>
@@ -13971,12 +14150,12 @@
         <v>520.81696648636103</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B467" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C467">
         <v>134.20634920634899</v>
@@ -13998,12 +14177,12 @@
         <v>688.71551574473199</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B468" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C468">
         <v>154.04761904761901</v>
@@ -14025,12 +14204,12 @@
         <v>1189.0832334946299</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B469" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C469">
         <v>182.619047619047</v>
@@ -14052,12 +14231,12 @@
         <v>1955.0555390100601</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B470" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C470">
         <v>41.349206349206298</v>
@@ -14079,12 +14258,12 @@
         <v>2.0175173385931702</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B471" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C471">
         <v>82.619047619047606</v>
@@ -14106,12 +14285,12 @@
         <v>41.375237018105402</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B472" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C472">
         <v>134.60317460317401</v>
@@ -14133,12 +14312,12 @@
         <v>249.04147906440599</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B473" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C473">
         <v>153.253968253968</v>
@@ -14160,12 +14339,12 @@
         <v>453.338949928906</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B474" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C474">
         <v>181.82539682539601</v>
@@ -14187,12 +14366,12 @@
         <v>923.40693950386697</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B475" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C475">
         <v>41.349206349206298</v>
@@ -14214,12 +14393,12 @@
         <v>6.9135482265033499</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B476" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C476">
         <v>81.825396825396794</v>
@@ -14241,12 +14420,12 @@
         <v>15.774342766336</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B477" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C477">
         <v>112.777777777777</v>
@@ -14268,12 +14447,12 @@
         <v>28.904366487440299</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B478" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C478">
         <v>153.65079365079299</v>
@@ -14295,12 +14474,12 @@
         <v>47.837792782336997</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B479" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C479">
         <v>183.809523809523</v>
@@ -14322,12 +14501,12 @@
         <v>83.050629948071006</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B480" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C480">
         <v>134.20634920634899</v>
@@ -14349,12 +14528,12 @@
         <v>448.73852437471999</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B481" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C481">
         <v>154.444444444444</v>
@@ -14376,12 +14555,12 @@
         <v>2031.7144993474001</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B482" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C482">
         <v>169.12698412698401</v>
@@ -14403,12 +14582,12 @@
         <v>4823.5884582773297</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B483" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C483">
         <v>182.619047619047</v>
@@ -14430,12 +14609,12 @@
         <v>9237.9945979315198</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B484" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C484">
         <v>83.412698412698404</v>
@@ -14457,12 +14636,12 @@
         <v>51.280035883796202</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B485" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C485">
         <v>111.587301587301</v>
@@ -14484,12 +14663,12 @@
         <v>57.944494917161599</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B486" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C486">
         <v>135</v>
@@ -14511,12 +14690,12 @@
         <v>52.716354194730201</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B487" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C487">
         <v>153.65079365079299</v>
@@ -14538,12 +14717,12 @@
         <v>81.720172141979106</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B488" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C488">
         <v>181.82539682539601</v>
@@ -14565,7 +14744,7 @@
         <v>134.33334578345401</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>237</v>
       </c>
@@ -14592,7 +14771,7 @@
         <v>1.1630826116569999</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>237</v>
       </c>
@@ -14619,7 +14798,7 @@
         <v>2.0388245596963994</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>237</v>
       </c>
@@ -14646,7 +14825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>237</v>
       </c>
@@ -14673,7 +14852,7 @@
         <v>41.447212221465101</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>237</v>
       </c>
@@ -14700,7 +14879,7 @@
         <v>1117.56378320521</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>237</v>
       </c>
@@ -14727,7 +14906,7 @@
         <v>1.1548195013025699</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>237</v>
       </c>
@@ -14754,7 +14933,7 @@
         <v>4.9880908075921102</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>237</v>
       </c>
@@ -14781,7 +14960,7 @@
         <v>12.9374767398585</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>237</v>
       </c>
@@ -14808,7 +14987,7 @@
         <v>33.4808336434685</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>237</v>
       </c>
@@ -14835,7 +15014,7 @@
         <v>32.848157796799399</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>239</v>
       </c>
@@ -14862,7 +15041,7 @@
         <v>2.7169652855542998</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>239</v>
       </c>
@@ -14889,7 +15068,7 @@
         <v>3.2362821948488198</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>239</v>
       </c>
@@ -14916,7 +15095,7 @@
         <v>5.12597984322508</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>239</v>
       </c>
@@ -14943,7 +15122,7 @@
         <v>11.279395296752501</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>242</v>
       </c>
@@ -14970,7 +15149,7 @@
         <v>1.66853303471444</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>242</v>
       </c>
@@ -14997,7 +15176,7 @@
         <v>2.0646696528555402</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>242</v>
       </c>
@@ -15024,7 +15203,7 @@
         <v>3.74160134378499</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>242</v>
       </c>
@@ -15051,7 +15230,7 @@
         <v>6.1744120940649401</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>239</v>
       </c>
@@ -15079,7 +15258,7 @@
         <v>1.56766381766381</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>239</v>
       </c>
@@ -15107,7 +15286,7 @@
         <v>2.0544871794871802</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>239</v>
       </c>
@@ -15135,7 +15314,7 @@
         <v>3.2628205128205101</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>239</v>
       </c>
@@ -15163,7 +15342,7 @@
         <v>4.8511396011396002</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>62</v>
       </c>
@@ -15190,7 +15369,7 @@
         <v>218.688060477927</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>62</v>
       </c>
@@ -15217,7 +15396,7 @@
         <v>44635.386560450599</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>62</v>
       </c>
@@ -15244,7 +15423,7 @@
         <v>339413.30524752499</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>62</v>
       </c>
@@ -15271,7 +15450,7 @@
         <v>311382.68605517503</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>64</v>
       </c>
@@ -15298,7 +15477,7 @@
         <v>89.599009159852798</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>64</v>
       </c>
@@ -15325,7 +15504,7 @@
         <v>2539.0118220981599</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>64</v>
       </c>
@@ -15352,7 +15531,7 @@
         <v>29470.5170255181</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>64</v>
       </c>
@@ -15379,7 +15558,7 @@
         <v>52199.655700525298</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>66</v>
       </c>
@@ -15406,7 +15585,7 @@
         <v>150.24256966487201</v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>66</v>
       </c>
@@ -15433,7 +15612,7 @@
         <v>38766.340899539602</v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>66</v>
       </c>
@@ -15460,7 +15639,7 @@
         <v>308718.51904743398</v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>66</v>
       </c>
@@ -15487,7 +15666,7 @@
         <v>358332.099618259</v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>62</v>
       </c>
@@ -15514,7 +15693,7 @@
         <v>80.662628855640307</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>62</v>
       </c>
@@ -15541,7 +15720,7 @@
         <v>372.75680879226701</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>62</v>
       </c>
@@ -15568,7 +15747,7 @@
         <v>252.809754923589</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>64</v>
       </c>
@@ -15595,7 +15774,7 @@
         <v>89.940235048733697</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>64</v>
       </c>
@@ -15622,7 +15801,7 @@
         <v>115.715374433435</v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>64</v>
       </c>
@@ -15649,7 +15828,7 @@
         <v>138.71084192370901</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>64</v>
       </c>
@@ -15676,7 +15855,7 @@
         <v>69.158878504672202</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>66</v>
       </c>
@@ -15703,7 +15882,7 @@
         <v>64.369660262322896</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>66</v>
       </c>
@@ -15730,7 +15909,7 @@
         <v>92.707873731497997</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>66</v>
       </c>
@@ -15757,12 +15936,12 @@
         <v>177.39761742408899</v>
       </c>
     </row>
-    <row r="533" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>243</v>
       </c>
       <c r="B533" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C533">
         <v>100</v>
@@ -15785,12 +15964,12 @@
         <v>1.8355423310855601</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>244</v>
       </c>
       <c r="B534" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C534">
         <v>100</v>
@@ -15813,12 +15992,12 @@
         <v>29.856026685612399</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>245</v>
       </c>
       <c r="B535" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C535">
         <v>100</v>
@@ -15841,12 +16020,12 @@
         <v>1.7980490564890901</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>243</v>
       </c>
       <c r="B536" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C536">
         <v>100</v>
@@ -15869,12 +16048,12 @@
         <v>51.360282136379098</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>244</v>
       </c>
       <c r="B537" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C537">
         <v>100</v>
@@ -15897,12 +16076,12 @@
         <v>83540.103002551798</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>245</v>
       </c>
       <c r="B538" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C538">
         <v>100</v>
@@ -15925,12 +16104,12 @@
         <v>6129.8801677706197</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>243</v>
       </c>
       <c r="B539" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C539">
         <v>100</v>
@@ -15953,12 +16132,12 @@
         <v>943.53847748515898</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>244</v>
       </c>
       <c r="B540" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C540">
         <v>100</v>
@@ -15981,12 +16160,12 @@
         <v>58943.061903343398</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>245</v>
       </c>
       <c r="B541" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C541">
         <v>100</v>
@@ -16009,12 +16188,12 @@
         <v>851.70355803861105</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>243</v>
       </c>
       <c r="B542" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C542">
         <v>100</v>
@@ -16037,12 +16216,12 @@
         <v>276.890268419591</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>244</v>
       </c>
       <c r="B543" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C543">
         <v>100</v>
@@ -16065,12 +16244,12 @@
         <v>19215.595418696201</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>245</v>
       </c>
       <c r="B544" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C544">
         <v>100</v>
@@ -16093,12 +16272,12 @@
         <v>4684.6060713342404</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>243</v>
       </c>
       <c r="B545" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C545">
         <v>100</v>
@@ -16120,12 +16299,12 @@
         <v>228.68947209403299</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>244</v>
       </c>
       <c r="B546" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C546">
         <v>100</v>
@@ -16147,12 +16326,12 @@
         <v>4808.1587537918404</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>245</v>
       </c>
       <c r="B547" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C547">
         <v>100</v>
@@ -16174,12 +16353,12 @@
         <v>9168.7176390797704</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>244</v>
       </c>
       <c r="B548" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C548">
         <v>100</v>
@@ -16202,12 +16381,12 @@
         <v>113.28734267102701</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>245</v>
       </c>
       <c r="B549" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C549">
         <v>100</v>
@@ -16230,12 +16409,12 @@
         <v>4130.6542609202297</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>244</v>
       </c>
       <c r="B550" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C550">
         <v>100</v>
@@ -16258,12 +16437,12 @@
         <v>54.750973553362897</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>245</v>
       </c>
       <c r="B551" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C551">
         <v>100</v>
@@ -16286,7 +16465,7 @@
         <v>7949.4988499372903</v>
       </c>
     </row>
-    <row r="552" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>246</v>
       </c>
@@ -16314,7 +16493,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>246</v>
       </c>
@@ -16342,7 +16521,7 @@
         <v>1408000</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>246</v>
       </c>
@@ -16370,7 +16549,7 @@
         <v>2818000</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>246</v>
       </c>
@@ -16398,7 +16577,7 @@
         <v>383.1</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>247</v>
       </c>
@@ -16426,7 +16605,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>247</v>
       </c>
@@ -16453,7 +16632,7 @@
         <v>582500</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>247</v>
       </c>
@@ -16481,7 +16660,7 @@
         <v>1658000</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>247</v>
       </c>
@@ -16509,7 +16688,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>248</v>
       </c>
@@ -16536,7 +16715,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>248</v>
       </c>
@@ -16563,7 +16742,7 @@
         <v>1327000</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>248</v>
       </c>
@@ -16590,7 +16769,7 @@
         <v>2031000</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>248</v>
       </c>
@@ -16617,7 +16796,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="564" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>253</v>
       </c>
@@ -16644,7 +16823,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>253</v>
       </c>
@@ -16671,7 +16850,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>253</v>
       </c>
@@ -16698,7 +16877,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>253</v>
       </c>
@@ -16725,7 +16904,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>253</v>
       </c>
@@ -16752,7 +16931,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>253</v>
       </c>
@@ -16779,7 +16958,7 @@
         <v>11.08</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>253</v>
       </c>
@@ -16806,7 +16985,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>253</v>
       </c>
@@ -16833,12 +17012,12 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B572" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C572">
         <v>50</v>
@@ -16860,12 +17039,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="573" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B573" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C573">
         <v>50</v>
@@ -16887,12 +17066,12 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B574" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C574">
         <v>50</v>
@@ -16914,12 +17093,12 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B575" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C575">
         <v>50</v>
@@ -16941,12 +17120,12 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B576" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C576">
         <v>50</v>
@@ -16968,12 +17147,12 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B577" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C577">
         <v>50</v>
@@ -16995,7 +17174,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="578" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>254</v>
       </c>
@@ -17022,7 +17201,7 @@
         <v>5.0159057620259704</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>254</v>
       </c>
@@ -17049,7 +17228,7 @@
         <v>569.714248726807</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>254</v>
       </c>
@@ -17076,7 +17255,7 @@
         <v>9415.084904314399</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>254</v>
       </c>
@@ -17103,7 +17282,7 @@
         <v>8913.8882713339208</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>254</v>
       </c>
@@ -17130,7 +17309,7 @@
         <v>6943.0128809192202</v>
       </c>
     </row>
-    <row r="583" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>256</v>
       </c>
@@ -17158,7 +17337,7 @@
         <v>2.7825594022071201</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>256</v>
       </c>
@@ -17186,7 +17365,7 @@
         <v>53.505085418733202</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>256</v>
       </c>
@@ -17214,7 +17393,7 @@
         <v>13287.913432286799</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>256</v>
       </c>
@@ -17242,7 +17421,7 @@
         <v>2035.3634682404199</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>256</v>
       </c>
@@ -17270,7 +17449,7 @@
         <v>1089.0229622637301</v>
       </c>
     </row>
-    <row r="588" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>258</v>
       </c>
@@ -17298,7 +17477,7 @@
         <v>1.3785225007599999</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>258</v>
       </c>
@@ -17326,7 +17505,7 @@
         <v>2.84346744757267</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>258</v>
       </c>
@@ -17354,7 +17533,7 @@
         <v>39.6453518087473</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>258</v>
       </c>
@@ -17382,7 +17561,7 @@
         <v>770.93409949018996</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>258</v>
       </c>
@@ -17410,7 +17589,7 @@
         <v>7374.0737605496997</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>258</v>
       </c>
@@ -17438,7 +17617,7 @@
         <v>5715.48201160394</v>
       </c>
     </row>
-    <row r="594" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>260</v>
       </c>
@@ -17465,7 +17644,7 @@
         <v>391.24095645155398</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>260</v>
       </c>
@@ -17492,7 +17671,7 @@
         <v>283569.69995563204</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>260</v>
       </c>
@@ -17519,7 +17698,7 @@
         <v>160148.616398871</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>260</v>
       </c>
@@ -17546,7 +17725,7 @@
         <v>81323.795818588391</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>260</v>
       </c>
@@ -17573,7 +17752,7 @@
         <v>31007.050317474299</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>260</v>
       </c>
@@ -17600,7 +17779,7 @@
         <v>20203.279233481102</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>260</v>
       </c>
@@ -17627,7 +17806,7 @@
         <v>241487.88800838901</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>260</v>
       </c>
@@ -17654,7 +17833,7 @@
         <v>141366.699530613</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>260</v>
       </c>
@@ -17681,7 +17860,7 @@
         <v>55880.915436266907</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>260</v>
       </c>
@@ -17708,7 +17887,7 @@
         <v>21322.938524639198</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>260</v>
       </c>
@@ -17735,7 +17914,7 @@
         <v>3213.7068680277603</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>260</v>
       </c>
@@ -17762,7 +17941,7 @@
         <v>41.373410807913601</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>260</v>
       </c>
